--- a/Base de Dados.xlsx
+++ b/Base de Dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Estudos\Desdobramento - Sigma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFBFE60D-5841-4C86-ADAA-DF14842F9BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F688004-7524-4CD3-A7AB-AC87897FC74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{052EBD17-0308-4E6D-95A6-CA02714B48B2}"/>
   </bookViews>
@@ -1678,9 +1678,6 @@
     <t>HBsAg</t>
   </si>
   <si>
-    <t>HbA1c</t>
-  </si>
-  <si>
     <t>IR</t>
   </si>
   <si>
@@ -2789,6 +2786,9 @@
   </si>
   <si>
     <t>5,7 - 6,4</t>
+  </si>
+  <si>
+    <t>HbA1c (D10)</t>
   </si>
 </sst>
 </file>
@@ -3704,10 +3704,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3728,10 +3728,10 @@
         <v>6</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -3760,7 +3760,7 @@
         <v>26.8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -3789,12 +3789,12 @@
         <v>75</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B4" s="1">
         <v>0.15</v>
@@ -3818,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3847,7 +3847,7 @@
         <v>46</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -3876,7 +3876,7 @@
         <v>0.99</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -3905,12 +3905,12 @@
         <v>0.3</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B8" s="1">
         <v>6.0999999999999999E-2</v>
@@ -3934,7 +3934,7 @@
         <v>5.2</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -3963,7 +3963,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -3992,12 +3992,12 @@
         <v>39.200000000000003</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B11" s="1">
         <v>0.18</v>
@@ -4021,12 +4021,12 @@
         <v>200</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B12" s="1">
         <v>0.2</v>
@@ -4041,7 +4041,7 @@
         <v>29</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -4070,12 +4070,12 @@
         <v>155</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B14" s="1">
         <v>0.2</v>
@@ -4090,7 +4090,7 @@
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -4119,7 +4119,7 @@
         <v>5.8</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -4148,7 +4148,7 @@
         <v>2.71</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -4177,12 +4177,12 @@
         <v>193</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B18" s="1">
         <v>0.19400000000000001</v>
@@ -4194,10 +4194,10 @@
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G18" s="2">
         <v>15</v>
@@ -4206,7 +4206,7 @@
         <v>99</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -4235,7 +4235,7 @@
         <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -4264,12 +4264,12 @@
         <v>1.07</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B21" s="1">
         <v>0.3</v>
@@ -4293,12 +4293,12 @@
         <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B22" s="1">
         <v>0.3</v>
@@ -4322,7 +4322,7 @@
         <v>9.99</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -4351,7 +4351,7 @@
         <v>0.99</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -4380,7 +4380,7 @@
         <v>60</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -4409,10 +4409,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -4441,7 +4441,7 @@
         <v>60</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -4470,7 +4470,7 @@
         <v>60</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
         <v>9.99</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4528,10 +4528,10 @@
         <v>0.89</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -4589,12 +4589,12 @@
         <v>24.9</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B32" s="1">
         <v>0.3</v>
@@ -4618,12 +4618,12 @@
         <v>114</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B33" s="1">
         <v>0.22</v>
@@ -4647,7 +4647,7 @@
         <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -4676,7 +4676,7 @@
         <v>304</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -4705,7 +4705,7 @@
         <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -4731,10 +4731,10 @@
         <v>6.99</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -4760,10 +4760,10 @@
         <v>6.99</v>
       </c>
       <c r="I37" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -4786,7 +4786,7 @@
         <v>100</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>103</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -4835,10 +4835,10 @@
         <v>6.99</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J40" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -4864,10 +4864,10 @@
         <v>6.99</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J41" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -4896,7 +4896,7 @@
         <v>77</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -4925,7 +4925,7 @@
         <v>0.78</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -4945,7 +4945,7 @@
         <v>115</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -4965,7 +4965,7 @@
         <v>117</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
@@ -4994,12 +4994,12 @@
         <v>5</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B47" s="1">
         <v>0.19400000000000001</v>
@@ -5011,10 +5011,10 @@
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F47" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G47" s="2">
         <v>0</v>
@@ -5023,7 +5023,7 @@
         <v>650</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -5052,7 +5052,7 @@
         <v>15</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -5081,7 +5081,7 @@
         <v>10</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -5110,12 +5110,12 @@
         <v>0.9</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B51" s="1">
         <v>0.155</v>
@@ -5139,7 +5139,7 @@
         <v>39</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -5168,7 +5168,7 @@
         <v>35</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -5197,7 +5197,7 @@
         <v>28.5</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -5226,7 +5226,7 @@
         <v>34</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -5255,7 +5255,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -5284,7 +5284,7 @@
         <v>6.9</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -5313,12 +5313,12 @@
         <v>225</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B58" s="1">
         <v>0.15</v>
@@ -5342,7 +5342,7 @@
         <v>9.6</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -5371,7 +5371,7 @@
         <v>1.4</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -5400,7 +5400,7 @@
         <v>14.3</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -5429,7 +5429,7 @@
         <v>50</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -5458,7 +5458,7 @@
         <v>130</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -5487,10 +5487,10 @@
         <v>13.99</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="J63" s="6" t="s">
         <v>882</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -5519,10 +5519,10 @@
         <v>9.99</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J64" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
@@ -5551,10 +5551,10 @@
         <v>9.99</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J65" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -5583,10 +5583,10 @@
         <v>8.99</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="J66" s="6" t="s">
         <v>885</v>
-      </c>
-      <c r="J66" s="6" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
@@ -5615,10 +5615,10 @@
         <v>0.89</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
@@ -5647,10 +5647,10 @@
         <v>6.99</v>
       </c>
       <c r="I68" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J68" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -5679,7 +5679,7 @@
         <v>3.8</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -5708,7 +5708,7 @@
         <v>60</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -5737,7 +5737,7 @@
         <v>0.99</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -5766,12 +5766,12 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B73" s="1">
         <v>0.25</v>
@@ -5783,10 +5783,10 @@
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F73" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G73" s="2">
         <v>100</v>
@@ -5795,12 +5795,12 @@
         <v>300</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B74" s="1">
         <v>0.13</v>
@@ -5824,12 +5824,12 @@
         <v>107</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B75" s="1">
         <v>0.1</v>
@@ -5841,10 +5841,10 @@
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F75" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G75" s="2">
         <v>110</v>
@@ -5853,7 +5853,7 @@
         <v>250</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
@@ -5882,10 +5882,10 @@
         <v>0.49</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="J76" s="6" t="s">
         <v>888</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -5914,10 +5914,10 @@
         <v>0.69</v>
       </c>
       <c r="I77" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="J77" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="J77" s="6" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -5946,7 +5946,7 @@
         <v>41</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5975,7 +5975,7 @@
         <v>360</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -6004,7 +6004,7 @@
         <v>150</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -6033,7 +6033,7 @@
         <v>170</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -6062,7 +6062,7 @@
         <v>36</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -6091,7 +6091,7 @@
         <v>22.45</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -6120,12 +6120,12 @@
         <v>20.29</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B85" s="1">
         <v>0.2</v>
@@ -6149,7 +6149,7 @@
         <v>1.17</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -6178,12 +6178,12 @@
         <v>120</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B87" s="1">
         <v>0.3</v>
@@ -6195,10 +6195,10 @@
         <v>7</v>
       </c>
       <c r="E87" t="s">
+        <v>723</v>
+      </c>
+      <c r="F87" t="s">
         <v>724</v>
-      </c>
-      <c r="F87" t="s">
-        <v>725</v>
       </c>
       <c r="G87" s="2">
         <v>39</v>
@@ -6207,7 +6207,7 @@
         <v>259</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -6236,10 +6236,10 @@
         <v>9.99</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J88" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -6268,7 +6268,7 @@
         <v>200</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -6297,10 +6297,10 @@
         <v>0.69</v>
       </c>
       <c r="I90" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="J90" s="6" t="s">
         <v>890</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -6329,10 +6329,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="J91" s="6" t="s">
         <v>893</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -6361,7 +6361,7 @@
         <v>138</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -6390,7 +6390,7 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -6410,7 +6410,7 @@
         <v>239</v>
       </c>
       <c r="F94" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G94" s="2">
         <v>0</v>
@@ -6419,15 +6419,15 @@
         <v>6.99</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B95" s="1">
         <v>0.2</v>
@@ -6451,7 +6451,7 @@
         <v>4.5</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -6480,7 +6480,7 @@
         <v>500</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6509,12 +6509,12 @@
         <v>1.2</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B98" s="1">
         <v>0.3</v>
@@ -6538,7 +6538,7 @@
         <v>345</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -6567,12 +6567,12 @@
         <v>199</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B100" s="1">
         <v>0.3</v>
@@ -6584,10 +6584,10 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F100" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G100" s="2">
         <v>40</v>
@@ -6596,12 +6596,12 @@
         <v>150</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B101" s="1">
         <v>0.13</v>
@@ -6625,7 +6625,7 @@
         <v>99</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -6654,7 +6654,7 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -6674,7 +6674,7 @@
         <v>263</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -6703,7 +6703,7 @@
         <v>115</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -6732,7 +6732,7 @@
         <v>129</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -6761,7 +6761,7 @@
         <v>3</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -6787,10 +6787,10 @@
         <v>6.99</v>
       </c>
       <c r="I107" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J107" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J107" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -6816,15 +6816,15 @@
         <v>6.99</v>
       </c>
       <c r="I108" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J108" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J108" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B109" s="1">
         <v>0.12</v>
@@ -6833,7 +6833,7 @@
         <v>0.06</v>
       </c>
       <c r="D109" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E109" t="s">
         <v>276</v>
@@ -6848,7 +6848,7 @@
         <v>99</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -6877,12 +6877,12 @@
         <v>60</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B111" s="1">
         <v>0.15</v>
@@ -6906,7 +6906,7 @@
         <v>500</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -6935,7 +6935,7 @@
         <v>0.89</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -6964,7 +6964,7 @@
         <v>200</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -6978,7 +6978,7 @@
         <v>286</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
@@ -6998,7 +6998,7 @@
         <v>289</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -7018,7 +7018,7 @@
         <v>289</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -7038,7 +7038,7 @@
         <v>291</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -7058,7 +7058,7 @@
         <v>293</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -7078,12 +7078,12 @@
         <v>295</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>546</v>
+        <v>916</v>
       </c>
       <c r="B120" s="1">
         <v>0.05</v>
@@ -7107,7 +7107,7 @@
         <v>5.6</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
@@ -7136,7 +7136,7 @@
         <v>0.99</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
@@ -7165,7 +7165,7 @@
         <v>0.9</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
@@ -7194,7 +7194,7 @@
         <v>60</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -7214,7 +7214,7 @@
         <v>309</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -7234,7 +7234,7 @@
         <v>312</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>0.9</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -7292,7 +7292,7 @@
         <v>0.9</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -7321,7 +7321,7 @@
         <v>0.99</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.25">
@@ -7350,7 +7350,7 @@
         <v>5</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
         <v>326</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.25">
@@ -7402,7 +7402,7 @@
         <v>350</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.25">
@@ -7422,7 +7422,7 @@
         <v>332</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.25">
@@ -7442,7 +7442,7 @@
         <v>334</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
         <v>336</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.25">
@@ -7491,7 +7491,7 @@
         <v>6.8</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <v>1600</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.25">
@@ -7546,7 +7546,7 @@
         <v>1011</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.25">
@@ -7572,7 +7572,7 @@
         <v>786</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.25">
@@ -7598,7 +7598,7 @@
         <v>85</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.25">
@@ -7624,7 +7624,7 @@
         <v>201</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.25">
@@ -7653,7 +7653,7 @@
         <v>300</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.25">
@@ -7682,7 +7682,7 @@
         <v>24.9</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.25">
@@ -7708,10 +7708,10 @@
         <v>6.99</v>
       </c>
       <c r="I143" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J143" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J143" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.25">
@@ -7731,7 +7731,7 @@
         <v>328</v>
       </c>
       <c r="F144" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G144" s="2">
         <v>170</v>
@@ -7740,7 +7740,7 @@
         <v>370</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.25">
@@ -7769,7 +7769,7 @@
         <v>22.4</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.25">
@@ -7795,10 +7795,10 @@
         <v>6.99</v>
       </c>
       <c r="I146" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J146" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J146" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.25">
@@ -7818,7 +7818,7 @@
         <v>330</v>
       </c>
       <c r="F147" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G147" s="2">
         <v>90</v>
@@ -7827,7 +7827,7 @@
         <v>210</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.25">
@@ -7856,12 +7856,12 @@
         <v>27</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B149" s="1">
         <v>0.25</v>
@@ -7885,7 +7885,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.25">
@@ -7914,7 +7914,7 @@
         <v>40</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.25">
@@ -7943,7 +7943,7 @@
         <v>8.6</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.25">
@@ -7972,12 +7972,12 @@
         <v>152</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B153" s="1">
         <v>0.3</v>
@@ -7989,10 +7989,10 @@
         <v>7</v>
       </c>
       <c r="E153" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F153" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G153" s="2">
         <v>4.0999999999999996</v>
@@ -8001,7 +8001,7 @@
         <v>13.8</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.25">
@@ -8030,12 +8030,12 @@
         <v>1.2</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B155" s="1">
         <v>0.1</v>
@@ -8059,12 +8059,12 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B156" s="1">
         <v>0.1</v>
@@ -8076,10 +8076,10 @@
         <v>7</v>
       </c>
       <c r="E156" t="s">
+        <v>732</v>
+      </c>
+      <c r="F156" t="s">
         <v>733</v>
-      </c>
-      <c r="F156" t="s">
-        <v>734</v>
       </c>
       <c r="G156" s="2">
         <v>17</v>
@@ -8088,7 +8088,7 @@
         <v>164</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.25">
@@ -8117,7 +8117,7 @@
         <v>2.5</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.25">
@@ -8143,10 +8143,10 @@
         <v>3.49</v>
       </c>
       <c r="I158" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="J158" s="6" t="s">
         <v>901</v>
-      </c>
-      <c r="J158" s="6" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.25">
@@ -8175,7 +8175,7 @@
         <v>9.99</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.25">
@@ -8204,7 +8204,7 @@
         <v>9.99</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
@@ -8233,7 +8233,7 @@
         <v>46</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
@@ -8262,7 +8262,7 @@
         <v>74.099999999999994</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
@@ -8291,10 +8291,10 @@
         <v>1.99</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
@@ -8323,10 +8323,10 @@
         <v>0.89</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
@@ -8355,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -8384,12 +8384,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B167" s="1">
         <v>0.25</v>
@@ -8413,12 +8413,12 @@
         <v>45</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B168" s="1">
         <v>0.12</v>
@@ -8442,7 +8442,7 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -8468,10 +8468,10 @@
         <v>1.99</v>
       </c>
       <c r="I169" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="J169" s="8" t="s">
         <v>907</v>
-      </c>
-      <c r="J169" s="8" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -8500,7 +8500,7 @@
         <v>40</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -8529,7 +8529,7 @@
         <v>15</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -8558,12 +8558,12 @@
         <v>17.7</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B173" s="1">
         <v>0.4</v>
@@ -8575,10 +8575,10 @@
         <v>7</v>
       </c>
       <c r="E173" t="s">
+        <v>735</v>
+      </c>
+      <c r="F173" t="s">
         <v>736</v>
-      </c>
-      <c r="F173" t="s">
-        <v>737</v>
       </c>
       <c r="G173" s="2">
         <v>1</v>
@@ -8587,7 +8587,7 @@
         <v>15</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -8616,12 +8616,12 @@
         <v>199</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B175" s="1">
         <v>0.05</v>
@@ -8645,7 +8645,7 @@
         <v>145</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -8674,7 +8674,7 @@
         <v>0.72</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.25">
@@ -8703,7 +8703,7 @@
         <v>0.06</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.25">
@@ -8726,7 +8726,7 @@
         <v>442</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.25">
@@ -8752,10 +8752,10 @@
         <v>6.99</v>
       </c>
       <c r="I179" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J179" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J179" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.25">
@@ -8781,10 +8781,10 @@
         <v>6.99</v>
       </c>
       <c r="I180" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J180" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J180" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.25">
@@ -8813,7 +8813,7 @@
         <v>9.99</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.25">
@@ -8842,10 +8842,10 @@
         <v>0.79</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.25">
@@ -8874,10 +8874,10 @@
         <v>13.49</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.25">
@@ -8906,10 +8906,10 @@
         <v>0.89</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.25">
@@ -8935,10 +8935,10 @@
         <v>6.99</v>
       </c>
       <c r="I185" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J185" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J185" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.25">
@@ -8967,7 +8967,7 @@
         <v>568.9</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.25">
@@ -8996,7 +8996,7 @@
         <v>76.7</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.25">
@@ -9022,15 +9022,15 @@
         <v>6.99</v>
       </c>
       <c r="I188" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J188" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J188" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B189" s="1">
         <v>0.1</v>
@@ -9042,10 +9042,10 @@
         <v>7</v>
       </c>
       <c r="E189" t="s">
+        <v>737</v>
+      </c>
+      <c r="F189" t="s">
         <v>738</v>
-      </c>
-      <c r="F189" t="s">
-        <v>739</v>
       </c>
       <c r="G189" s="2">
         <v>18</v>
@@ -9054,12 +9054,12 @@
         <v>301</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B190" s="1">
         <v>0.18</v>
@@ -9083,7 +9083,7 @@
         <v>48.5</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.25">
@@ -9112,7 +9112,7 @@
         <v>225</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.25">
@@ -9141,7 +9141,7 @@
         <v>0.99</v>
       </c>
       <c r="I192" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
@@ -9170,7 +9170,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.25">
@@ -9199,7 +9199,7 @@
         <v>0.95</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.25">
@@ -9228,7 +9228,7 @@
         <v>200</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.25">
@@ -9257,7 +9257,7 @@
         <v>1.68</v>
       </c>
       <c r="I196" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
@@ -9286,7 +9286,7 @@
         <v>12.1</v>
       </c>
       <c r="I197" s="3" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.25">
@@ -9315,7 +9315,7 @@
         <v>39</v>
       </c>
       <c r="I198" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.25">
@@ -9344,7 +9344,7 @@
         <v>740</v>
       </c>
       <c r="I199" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.25">
@@ -9373,7 +9373,7 @@
         <v>740</v>
       </c>
       <c r="I200" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.25">
@@ -9402,12 +9402,12 @@
         <v>308</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B202" s="1">
         <v>0.12</v>
@@ -9431,7 +9431,7 @@
         <v>5.2</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="203" spans="1:10" x14ac:dyDescent="0.25">
@@ -9460,7 +9460,7 @@
         <v>77</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.25">
@@ -9489,10 +9489,10 @@
         <v>0.99</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J204" s="6" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.25">
@@ -9521,10 +9521,10 @@
         <v>0.79</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J205" s="6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.25">
@@ -9553,7 +9553,7 @@
         <v>1.75</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
@@ -9582,7 +9582,7 @@
         <v>60</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.25">
@@ -9611,7 +9611,7 @@
         <v>7.6</v>
       </c>
       <c r="I208" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.25">
@@ -9640,7 +9640,7 @@
         <v>4.2</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.25">
@@ -9660,7 +9660,7 @@
         <v>521</v>
       </c>
       <c r="F210" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
@@ -9669,10 +9669,10 @@
         <v>6.99</v>
       </c>
       <c r="I210" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J210" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J210" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.25">
@@ -9692,7 +9692,7 @@
         <v>523</v>
       </c>
       <c r="F211" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
@@ -9701,10 +9701,10 @@
         <v>6.99</v>
       </c>
       <c r="I211" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="J211" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="J211" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.25">
@@ -9733,12 +9733,12 @@
         <v>200</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B213" s="1">
         <v>0.221</v>
@@ -9750,10 +9750,10 @@
         <v>7</v>
       </c>
       <c r="E213" t="s">
+        <v>740</v>
+      </c>
+      <c r="F213" t="s">
         <v>741</v>
-      </c>
-      <c r="F213" t="s">
-        <v>742</v>
       </c>
       <c r="G213" s="2">
         <v>12</v>
@@ -9762,7 +9762,7 @@
         <v>20</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.25">
@@ -9791,7 +9791,7 @@
         <v>150</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.25">
@@ -9820,10 +9820,10 @@
         <v>0.89</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="J215" s="6" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
@@ -9852,7 +9852,7 @@
         <v>771</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.25">
@@ -9881,7 +9881,7 @@
         <v>100</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -9910,7 +9910,7 @@
         <v>79.3</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
@@ -9939,12 +9939,12 @@
         <v>285</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B220" s="5">
         <v>5.5E-2</v>
@@ -9956,10 +9956,10 @@
         <v>311</v>
       </c>
       <c r="E220" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G220" s="2">
         <v>4</v>
@@ -9974,7 +9974,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B221" s="5">
         <v>0.12</v>
@@ -9986,10 +9986,10 @@
         <v>311</v>
       </c>
       <c r="E221" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G221" s="2">
         <v>4</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B222" s="5">
         <v>0.17499999999999999</v>
@@ -10016,10 +10016,10 @@
         <v>311</v>
       </c>
       <c r="E222" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G222" s="2">
         <v>1.48</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B223" s="5">
         <v>0.17599999999999999</v>
@@ -10046,10 +10046,10 @@
         <v>311</v>
       </c>
       <c r="E223" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G223" s="2">
         <v>0.74</v>
@@ -10064,7 +10064,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B224" s="5">
         <v>0.27900000000000003</v>
@@ -10076,10 +10076,10 @@
         <v>311</v>
       </c>
       <c r="E224" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G224" s="2">
         <v>0.37</v>
@@ -10094,7 +10094,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B225" s="5">
         <v>0.29699999999999999</v>
@@ -10106,10 +10106,10 @@
         <v>311</v>
       </c>
       <c r="E225" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G225" s="2">
         <v>0</v>
@@ -10124,7 +10124,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B226" s="5">
         <v>0.27300000000000002</v>
@@ -10136,10 +10136,10 @@
         <v>311</v>
       </c>
       <c r="E226" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G226" s="2">
         <v>0</v>
@@ -10154,7 +10154,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B227" s="5">
         <v>0.13439999999999999</v>
@@ -10166,10 +10166,10 @@
         <v>311</v>
       </c>
       <c r="E227" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G227" s="2">
         <v>130</v>
@@ -10184,7 +10184,7 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B228" s="5">
         <v>0.14979999999999999</v>
@@ -10196,10 +10196,10 @@
         <v>311</v>
       </c>
       <c r="E228" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G228" s="2">
         <v>0.9</v>
@@ -10214,7 +10214,7 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B229" s="5">
         <v>0.22800000000000001</v>
@@ -10226,10 +10226,10 @@
         <v>311</v>
       </c>
       <c r="E229" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G229" s="2">
         <v>0.59</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B230" s="5">
         <v>0.627</v>
@@ -10256,10 +10256,10 @@
         <v>311</v>
       </c>
       <c r="E230" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G230" s="2">
         <v>1.57</v>
@@ -10274,7 +10274,7 @@
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B231" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10286,10 +10286,10 @@
         <v>311</v>
       </c>
       <c r="E231" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F231" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G231" s="2">
         <v>13</v>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B232" s="5">
         <v>7.5200000000000003E-2</v>
@@ -10316,10 +10316,10 @@
         <v>311</v>
       </c>
       <c r="E232" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G232" s="2">
         <v>30.6</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B233" s="5">
         <v>0.15</v>
@@ -10346,10 +10346,10 @@
         <v>311</v>
       </c>
       <c r="E233" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G233" s="2">
         <v>0</v>
@@ -10364,7 +10364,7 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B234" s="5">
         <v>0.2979</v>
@@ -10376,17 +10376,17 @@
         <v>311</v>
       </c>
       <c r="E234" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G234"/>
       <c r="H234"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B235" s="5">
         <v>5.8000000000000003E-2</v>
@@ -10398,10 +10398,10 @@
         <v>311</v>
       </c>
       <c r="E235" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G235" s="2">
         <v>36</v>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B236" s="5">
         <v>0.06</v>
@@ -10428,10 +10428,10 @@
         <v>311</v>
       </c>
       <c r="E236" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G236" s="2">
         <v>80</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B237" s="5">
         <v>5.5E-2</v>
@@ -10458,10 +10458,10 @@
         <v>311</v>
       </c>
       <c r="E237" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G237" s="2">
         <v>26.8</v>
@@ -10476,7 +10476,7 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B238" s="5">
         <v>7.4999999999999997E-2</v>
@@ -10488,10 +10488,10 @@
         <v>311</v>
       </c>
       <c r="E238" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G238" s="2">
         <v>30</v>
@@ -10506,7 +10506,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B239" s="5">
         <v>4.5600000000000002E-2</v>
@@ -10518,10 +10518,10 @@
         <v>311</v>
       </c>
       <c r="E239" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G239" s="2">
         <v>11</v>
@@ -10536,7 +10536,7 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B240" s="5">
         <v>0.16</v>
@@ -10548,10 +10548,10 @@
         <v>311</v>
       </c>
       <c r="E240" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G240" s="2">
         <v>130</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B241" s="5">
         <v>8.7999999999999995E-2</v>
@@ -10578,10 +10578,10 @@
         <v>311</v>
       </c>
       <c r="E241" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G241" s="2">
         <v>6.8</v>
@@ -10596,7 +10596,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
-        <v>850</v>
+        <v>300</v>
       </c>
       <c r="B242" s="5">
         <v>0.05</v>
@@ -10608,10 +10608,10 @@
         <v>311</v>
       </c>
       <c r="E242" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G242" s="2">
         <v>0</v>
@@ -10624,7 +10624,7 @@
         <v>0 - 5,69</v>
       </c>
       <c r="J242" s="6" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -10823,17 +10823,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -10843,37 +10843,37 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -10883,282 +10883,282 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
@@ -11173,12 +11173,12 @@
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
@@ -11188,27 +11188,27 @@
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
@@ -11223,47 +11223,47 @@
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
   </sheetData>
